--- a/artfynd/A 32818-2024 artfynd.xlsx
+++ b/artfynd/A 32818-2024 artfynd.xlsx
@@ -1344,7 +1344,7 @@
         <v>119796459</v>
       </c>
       <c r="B8" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 32818-2024 artfynd.xlsx
+++ b/artfynd/A 32818-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118675912</v>
+        <v>118675908</v>
       </c>
       <c r="B2" t="n">
-        <v>79574</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>740539</v>
+        <v>740645</v>
       </c>
       <c r="R2" t="n">
-        <v>7286640</v>
+        <v>7286503</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118675910</v>
+        <v>118675909</v>
       </c>
       <c r="B3" t="n">
-        <v>79574</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -830,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>740599</v>
+        <v>740601</v>
       </c>
       <c r="R3" t="n">
-        <v>7286463</v>
+        <v>7286407</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118675916</v>
+        <v>118675910</v>
       </c>
       <c r="B4" t="n">
-        <v>79574</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>740567</v>
+        <v>740599</v>
       </c>
       <c r="R4" t="n">
-        <v>7286429</v>
+        <v>7286463</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1008,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118675908</v>
+        <v>118675912</v>
       </c>
       <c r="B5" t="n">
-        <v>79574</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1052,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>740645</v>
+        <v>740539</v>
       </c>
       <c r="R5" t="n">
-        <v>7286503</v>
+        <v>7286640</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,37 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118675913</v>
+        <v>118675916</v>
       </c>
       <c r="B6" t="n">
-        <v>79603</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>740767</v>
+        <v>740567</v>
       </c>
       <c r="R6" t="n">
-        <v>7286299</v>
+        <v>7286429</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,12 +1168,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1230,15 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118675909</v>
+        <v>119796459</v>
       </c>
       <c r="B7" t="n">
-        <v>79574</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>740601</v>
+        <v>740595</v>
       </c>
       <c r="R7" t="n">
-        <v>7286407</v>
+        <v>7286470</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,12 +1274,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1341,37 +1311,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119796459</v>
+        <v>118675913</v>
       </c>
       <c r="B8" t="n">
-        <v>79623</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>740595</v>
+        <v>740767</v>
       </c>
       <c r="R8" t="n">
-        <v>7286470</v>
+        <v>7286299</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,12 +1380,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">

--- a/artfynd/A 32818-2024 artfynd.xlsx
+++ b/artfynd/A 32818-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118675908</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118675909</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118675910</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118675912</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118675916</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119796459</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,8 +1449,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118675913</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>